--- a/tabelas_classes_excel/Tabela_3-14_O_Monge.xlsx
+++ b/tabelas_classes_excel/Tabela_3-14_O_Monge.xlsx
@@ -684,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -737,31 +737,6 @@
           <t>C7</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>C8</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>C10</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>C11</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>C12</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -773,1023 +748,672 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bônus Base</t>
+          <t>Nível</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bônus de Ataque da</t>
+          <t>Bônus Base de Ataque</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dano</t>
+          <t>Fortitude</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bôn</t>
+          <t>Reflexos</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Vontade</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Especial</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nível de Ataque Fortitude Reflexos Vontade Especial</t>
+          <t>1°</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rajada de Golpes Desarmado* na</t>
+          <t>+0</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talento adicional, rajada de golpes, ataque | –2/–2 1d6 +0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Talento adicional, rajada de golpes, ataque</t>
+          <t>2°</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talento adicional, evasão –1/–1 1d6 +0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3°</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+0</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>–2/–2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1d6</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>+0</t>
+          <t>Mente tranqüila +0/+0 1d6 +0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>desarmado</t>
+          <t>4°</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>+4</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+4</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>+4</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ataque chi (mágico), queda suave 6 m +1/+1 1d8 +0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5°</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talento adicional, evasão</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>–1/–1</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>1d6</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>+0</t>
+          <t>Pureza corporal +2/+2 1d8 +1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6°</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mente tranqüila</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>+0/+0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1d6</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>+0</t>
+          <t>Talento adicional, queda suave 9 m +3/+3 1d8 +1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4°</t>
+          <t>7°</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ataque chi (mágico), queda suave 6 m</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>+1/+1</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1d8</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>+0</t>
+          <t>Integridade corporal +4/+4 1d8 +1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5°</t>
+          <t>8°</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+6/+1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pureza corporal</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>+2/+2</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1d8</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>+1</t>
+          <t>Queda suave 12 m +5/+5/+0 1d10 +1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6°</t>
+          <t>9°</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+6/+1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talento adicional, queda suave 9 m</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>+3/+3</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1d8</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>+1</t>
+          <t>Evasão aprimorada +6/+6/+1 1d10 +1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7°</t>
+          <t>10°</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+7/+2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Integridade corporal</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>+4/+4</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>1d8</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>+1</t>
+          <t>Ataque chi (ordem). Queda suave 15 m +7/+7/+2 1d10 +2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8°</t>
+          <t>11°</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+6/+1</t>
+          <t>+8/+3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Queda suave 12 m</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>+5/+5/+0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>1d10</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>+1</t>
+          <t>Corpo de diamante, rajada maior +8/+8/+8/+3 1d10 +2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9°</t>
+          <t>12°</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>+6/+1</t>
+          <t>+9/+4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Evasão aprimorada</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>+6/+6/+1</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>1d10</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>+1</t>
+          <t>Passo etéreo, queda suave 18 m +9/+9/+9/+4 2d6 +2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10°</t>
+          <t>13°</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>+7/+2</t>
+          <t>+9/+4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ataque chi (ordem). Queda suave 15 m</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>+7/+7/+2</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>1d10</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>+2</t>
+          <t>Alma de diamante +9/+9/+9/+4 2d6 +2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>11°</t>
+          <t>14°</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>+8/+3</t>
+          <t>+10/+5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Corpo de diamante, rajada maior</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>+8/+8/+8/+3</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>1d10</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>+2</t>
+          <t>Queda suave 21 m +10/+10/+10/+5 2d6 +2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>12°</t>
+          <t>15°</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>+9/+4</t>
+          <t>+11/+6/+1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Passo etéreo, queda suave 18 m</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>+9/+9/+9/+4</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2d6</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>+2</t>
+          <t>Mão vibrante +11/+11/+11/+6/+1 2d6 +3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>13°</t>
+          <t>16°</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>+9/+4</t>
+          <t>+12/+7/+2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Alma de diamante</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>+9/+9/+9/+4</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2d6</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>+2</t>
+          <t>Ataque chi (adamante), queda suave 24 m +12/+12/+12/+7/+2 2d8 +3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>14°</t>
+          <t>17°</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>+10/+5</t>
+          <t>+12/+7/+2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Queda suave 21 m</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>+10/+10/+10/+5</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2d6</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>+2</t>
+          <t>Corpo atemporal, idiomas do sol e da lua +12/+12/+12/+7/+2 2d8 +3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>15° +11/+6/+1</t>
+          <t>18°</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+13/+8/+3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mão vibrante</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+11/+11/+11/+6/+1</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2d6</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>+3</t>
+          <t>Queda suave 27 m +13/+13/+13/+8/+3 2d8 +3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>16° +12/+7/+2</t>
+          <t>19°</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+14/+9/+4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>+10 Ataque chi (adamante), queda suave 24 m +12/+12/+12/+7/+2</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2d8</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>Corpo vazio +14/+14/+14/+9/+4 2d8 +3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>17° +12/+7/+2</t>
+          <t>20°</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+15/+10/+5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+12</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>+10 Corpo atemporal, idiomas do sol e da lua</t>
+          <t>+12</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>+12/+12/+12/+7/+2</t>
+          <t>+12</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2d8</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>18° +13/+8/+3</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>+11</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>+11</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>+11 Queda suave 27 m</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>+13/+13/+13/+8/+3</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2d8</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>19° +14/+9/+4</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>+11</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>+11</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>+11 Corpo vazio</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>+14/+14/+14/+9/+4</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2d8</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Auto-perfeição, queda suave qualquer</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>20° +15/+10/+5</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>+12</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>+12</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>+12</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>+15/+15/+15/+10/+5</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2d10</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>+4</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>distância</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>* Este valor considera monges Médios. Veja a tabela a Tabela 3-15: Dano Desarmado de Monges Pequenos e Grandes para obte</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Um monge causa mais dano com seu ataque desarmado que uma pessoa normal,</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Alma de Diamante (Ext): A p</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>conforme indicado na Tabela 3-14: O Monge. O dano de ataque desarmado dessa</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>à Magia equivalente ao seu nível</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>tabela considera monges Médios. Um monge Pequeno causa um dano inferior ao</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>magia, um conjurador precisa obt</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>valor indicado com seu ataque desarmado, enquanto os monges Grandes causam</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>nível de conjurador; consulte Re</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>um dano superior, conforme descrito na Tabela 3-15: Dano Desarmado de Monges</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>à Magia do monge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Pequenos e Grandes.</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Mão Vibrante (Sob): A parti</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ções no interior do corpo de out</t>
+          <t>Auto-perfeição, queda suave qualquer | +15/+15/+15/+10/+5 2d10 +4</t>
         </is>
       </c>
     </row>
